--- a/Payment.xlsx
+++ b/Payment.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\project\exel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CF81B16-89B0-4C63-ACF5-5EC28C37C27F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE8F46C-7C1F-41A6-B467-D730E10D7A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -259,7 +259,7 @@
       <name val="Arial Unicode MS"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -272,8 +272,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -281,19 +287,51 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -577,1789 +615,1793 @@
   <dimension ref="A1:I55"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="19.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="16.44140625" customWidth="1"/>
-    <col min="8" max="8" width="20.77734375" customWidth="1"/>
+    <col min="1" max="1" width="19.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="16.44140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="20.77734375" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="3">
         <v>42</v>
       </c>
-      <c r="D2">
-        <v>40</v>
-      </c>
-      <c r="E2" s="2">
+      <c r="D2" s="3">
+        <v>40</v>
+      </c>
+      <c r="E2" s="5">
         <v>12</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="5">
         <f>C2*E2</f>
         <v>504</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="6">
         <f>IF(C2&gt;40,C2-40,0)</f>
         <v>2</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="5">
         <f>G2*E2/2</f>
         <v>12</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="8">
         <f>F2+H2</f>
         <v>516</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="3">
         <v>38</v>
       </c>
-      <c r="D3">
-        <v>40</v>
-      </c>
-      <c r="E3" s="2">
+      <c r="D3" s="3">
+        <v>40</v>
+      </c>
+      <c r="E3" s="5">
         <v>10</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="5">
         <f t="shared" ref="F3:F51" si="0">C3*E3</f>
         <v>380</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="6">
         <f t="shared" ref="G3:G51" si="1">IF(C3&gt;40,C3-40,0)</f>
         <v>0</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="5">
         <f t="shared" ref="H3:H51" si="2">G3*E3/2</f>
         <v>0</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="8">
         <f t="shared" ref="I3:I51" si="3">F3+H3</f>
         <v>380</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C4">
-        <v>40</v>
-      </c>
-      <c r="D4">
-        <v>40</v>
-      </c>
-      <c r="E4" s="2">
+      <c r="C4" s="3">
+        <v>40</v>
+      </c>
+      <c r="D4" s="3">
+        <v>40</v>
+      </c>
+      <c r="E4" s="5">
         <v>9</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="5">
         <f t="shared" si="0"/>
         <v>360</v>
       </c>
-      <c r="G4" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H4" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I4" s="2">
+      <c r="G4" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I4" s="8">
         <f t="shared" si="3"/>
         <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" t="s">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="3">
         <v>45</v>
       </c>
-      <c r="D5">
-        <v>40</v>
-      </c>
-      <c r="E5" s="2">
+      <c r="D5" s="3">
+        <v>40</v>
+      </c>
+      <c r="E5" s="5">
         <v>15</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="5">
         <f t="shared" si="0"/>
         <v>675</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="6">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="5">
         <f t="shared" si="2"/>
         <v>37.5</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="8">
         <f t="shared" si="3"/>
         <v>712.5</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" t="s">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="3">
         <v>41</v>
       </c>
-      <c r="D6">
-        <v>40</v>
-      </c>
-      <c r="E6" s="2">
+      <c r="D6" s="3">
+        <v>40</v>
+      </c>
+      <c r="E6" s="5">
         <v>12</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="5">
         <f t="shared" si="0"/>
         <v>492</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="6">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="5">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="8">
         <f t="shared" si="3"/>
         <v>498</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" t="s">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="3">
         <v>39</v>
       </c>
-      <c r="D7">
-        <v>40</v>
-      </c>
-      <c r="E7" s="2">
+      <c r="D7" s="3">
+        <v>40</v>
+      </c>
+      <c r="E7" s="5">
         <v>8</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="5">
         <f t="shared" si="0"/>
         <v>312</v>
       </c>
-      <c r="G7" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="G7" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I7" s="8">
         <f t="shared" si="3"/>
         <v>312</v>
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" t="s">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="3">
         <v>44</v>
       </c>
-      <c r="D8">
-        <v>40</v>
-      </c>
-      <c r="E8" s="2">
+      <c r="D8" s="3">
+        <v>40</v>
+      </c>
+      <c r="E8" s="5">
         <v>13</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="5">
         <f t="shared" si="0"/>
         <v>572</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="6">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="5">
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="8">
         <f t="shared" si="3"/>
         <v>598</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" t="s">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="3">
         <v>37</v>
       </c>
-      <c r="D9">
-        <v>40</v>
-      </c>
-      <c r="E9" s="2">
+      <c r="D9" s="3">
+        <v>40</v>
+      </c>
+      <c r="E9" s="5">
         <v>10</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="5">
         <f t="shared" si="0"/>
         <v>370</v>
       </c>
-      <c r="G9" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="2">
+      <c r="G9" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="8">
         <f t="shared" si="3"/>
         <v>370</v>
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" t="s">
+      <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C10">
-        <v>40</v>
-      </c>
-      <c r="D10">
-        <v>40</v>
-      </c>
-      <c r="E10" s="2">
+      <c r="C10" s="3">
+        <v>40</v>
+      </c>
+      <c r="D10" s="3">
+        <v>40</v>
+      </c>
+      <c r="E10" s="5">
         <v>8</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="5">
         <f t="shared" si="0"/>
         <v>320</v>
       </c>
-      <c r="G10" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="2">
+      <c r="G10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="8">
         <f t="shared" si="3"/>
         <v>320</v>
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" t="s">
+      <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="3">
         <v>43</v>
       </c>
-      <c r="D11">
-        <v>40</v>
-      </c>
-      <c r="E11" s="2">
+      <c r="D11" s="3">
+        <v>40</v>
+      </c>
+      <c r="E11" s="5">
         <v>12</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="5">
         <f t="shared" si="0"/>
         <v>516</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="6">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="5">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="8">
         <f t="shared" si="3"/>
         <v>534</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" t="s">
+      <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="3">
         <v>46</v>
       </c>
-      <c r="D12">
-        <v>40</v>
-      </c>
-      <c r="E12" s="2">
+      <c r="D12" s="3">
+        <v>40</v>
+      </c>
+      <c r="E12" s="5">
         <v>16</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="5">
         <f t="shared" si="0"/>
         <v>736</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="6">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="5">
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="8">
         <f t="shared" si="3"/>
         <v>784</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" t="s">
+      <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C13">
-        <v>40</v>
-      </c>
-      <c r="D13">
-        <v>40</v>
-      </c>
-      <c r="E13" s="2">
+      <c r="C13" s="3">
+        <v>40</v>
+      </c>
+      <c r="D13" s="3">
+        <v>40</v>
+      </c>
+      <c r="E13" s="5">
         <v>9</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="5">
         <f t="shared" si="0"/>
         <v>360</v>
       </c>
-      <c r="G13" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H13" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I13" s="2">
+      <c r="G13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="8">
         <f t="shared" si="3"/>
         <v>360</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" t="s">
+      <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="3">
         <v>36</v>
       </c>
-      <c r="D14">
-        <v>40</v>
-      </c>
-      <c r="E14" s="2">
+      <c r="D14" s="3">
+        <v>40</v>
+      </c>
+      <c r="E14" s="5">
         <v>8</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="5">
         <f t="shared" si="0"/>
         <v>288</v>
       </c>
-      <c r="G14" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="2">
+      <c r="G14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="8">
         <f t="shared" si="3"/>
         <v>288</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" t="s">
+      <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="3">
         <v>42</v>
       </c>
-      <c r="D15">
-        <v>40</v>
-      </c>
-      <c r="E15" s="2">
+      <c r="D15" s="3">
+        <v>40</v>
+      </c>
+      <c r="E15" s="5">
         <v>13</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="5">
         <f t="shared" si="0"/>
         <v>546</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="6">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="5">
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I15" s="8">
         <f t="shared" si="3"/>
         <v>559</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" t="s">
+      <c r="A16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="3">
         <v>38</v>
       </c>
-      <c r="D16">
-        <v>40</v>
-      </c>
-      <c r="E16" s="2">
+      <c r="D16" s="3">
+        <v>40</v>
+      </c>
+      <c r="E16" s="5">
         <v>10</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="5">
         <f t="shared" si="0"/>
         <v>380</v>
       </c>
-      <c r="G16" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="2">
+      <c r="G16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="8">
         <f t="shared" si="3"/>
         <v>380</v>
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" t="s">
+      <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="3">
         <v>41</v>
       </c>
-      <c r="D17">
-        <v>40</v>
-      </c>
-      <c r="E17" s="2">
+      <c r="D17" s="3">
+        <v>40</v>
+      </c>
+      <c r="E17" s="5">
         <v>12</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="5">
         <f t="shared" si="0"/>
         <v>492</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="6">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="5">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17" s="8">
         <f t="shared" si="3"/>
         <v>498</v>
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" t="s">
+      <c r="A18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="3">
         <v>39</v>
       </c>
-      <c r="D18">
-        <v>40</v>
-      </c>
-      <c r="E18" s="2">
+      <c r="D18" s="3">
+        <v>40</v>
+      </c>
+      <c r="E18" s="5">
         <v>8</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="5">
         <f t="shared" si="0"/>
         <v>312</v>
       </c>
-      <c r="G18" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H18" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I18" s="2">
+      <c r="G18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="8">
         <f t="shared" si="3"/>
         <v>312</v>
       </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" t="s">
+      <c r="A19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C19">
-        <v>40</v>
-      </c>
-      <c r="D19">
-        <v>40</v>
-      </c>
-      <c r="E19" s="2">
+      <c r="C19" s="3">
+        <v>40</v>
+      </c>
+      <c r="D19" s="3">
+        <v>40</v>
+      </c>
+      <c r="E19" s="5">
         <v>9</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="5">
         <f t="shared" si="0"/>
         <v>360</v>
       </c>
-      <c r="G19" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H19" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I19" s="2">
+      <c r="G19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H19" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I19" s="8">
         <f t="shared" si="3"/>
         <v>360</v>
       </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" t="s">
+      <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="3">
         <v>43</v>
       </c>
-      <c r="D20">
-        <v>40</v>
-      </c>
-      <c r="E20" s="2">
+      <c r="D20" s="3">
+        <v>40</v>
+      </c>
+      <c r="E20" s="5">
         <v>12</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="5">
         <f t="shared" si="0"/>
         <v>516</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="6">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20" s="5">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="I20" s="2">
+      <c r="I20" s="8">
         <f t="shared" si="3"/>
         <v>534</v>
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" t="s">
+      <c r="A21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="3">
         <v>37</v>
       </c>
-      <c r="D21">
-        <v>40</v>
-      </c>
-      <c r="E21" s="2">
+      <c r="D21" s="3">
+        <v>40</v>
+      </c>
+      <c r="E21" s="5">
         <v>10</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="5">
         <f t="shared" si="0"/>
         <v>370</v>
       </c>
-      <c r="G21" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I21" s="2">
+      <c r="G21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="8">
         <f t="shared" si="3"/>
         <v>370</v>
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" t="s">
+      <c r="A22" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C22">
-        <v>40</v>
-      </c>
-      <c r="D22">
-        <v>40</v>
-      </c>
-      <c r="E22" s="2">
+      <c r="C22" s="3">
+        <v>40</v>
+      </c>
+      <c r="D22" s="3">
+        <v>40</v>
+      </c>
+      <c r="E22" s="5">
         <v>8</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="5">
         <f t="shared" si="0"/>
         <v>320</v>
       </c>
-      <c r="G22" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H22" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I22" s="2">
+      <c r="G22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H22" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I22" s="8">
         <f t="shared" si="3"/>
         <v>320</v>
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" t="s">
+      <c r="A23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="3">
         <v>44</v>
       </c>
-      <c r="D23">
-        <v>40</v>
-      </c>
-      <c r="E23" s="2">
+      <c r="D23" s="3">
+        <v>40</v>
+      </c>
+      <c r="E23" s="5">
         <v>13</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="5">
         <f t="shared" si="0"/>
         <v>572</v>
       </c>
-      <c r="G23" s="3">
+      <c r="G23" s="6">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23" s="5">
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
-      <c r="I23" s="2">
+      <c r="I23" s="8">
         <f t="shared" si="3"/>
         <v>598</v>
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" t="s">
+      <c r="A24" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="3">
         <v>45</v>
       </c>
-      <c r="D24">
-        <v>40</v>
-      </c>
-      <c r="E24" s="2">
+      <c r="D24" s="3">
+        <v>40</v>
+      </c>
+      <c r="E24" s="5">
         <v>15</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="5">
         <f t="shared" si="0"/>
         <v>675</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="6">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24" s="5">
         <f t="shared" si="2"/>
         <v>37.5</v>
       </c>
-      <c r="I24" s="2">
+      <c r="I24" s="8">
         <f t="shared" si="3"/>
         <v>712.5</v>
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" t="s">
+      <c r="A25" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C25">
-        <v>40</v>
-      </c>
-      <c r="D25">
-        <v>40</v>
-      </c>
-      <c r="E25" s="2">
+      <c r="C25" s="3">
+        <v>40</v>
+      </c>
+      <c r="D25" s="3">
+        <v>40</v>
+      </c>
+      <c r="E25" s="5">
         <v>9</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="5">
         <f t="shared" si="0"/>
         <v>360</v>
       </c>
-      <c r="G25" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H25" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I25" s="2">
+      <c r="G25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H25" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I25" s="8">
         <f t="shared" si="3"/>
         <v>360</v>
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" t="s">
+      <c r="A26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="3">
         <v>38</v>
       </c>
-      <c r="D26">
-        <v>40</v>
-      </c>
-      <c r="E26" s="2">
+      <c r="D26" s="3">
+        <v>40</v>
+      </c>
+      <c r="E26" s="5">
         <v>8</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="5">
         <f t="shared" si="0"/>
         <v>304</v>
       </c>
-      <c r="G26" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H26" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I26" s="2">
+      <c r="G26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="8">
         <f t="shared" si="3"/>
         <v>304</v>
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" t="s">
+      <c r="A27" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="3">
         <v>42</v>
       </c>
-      <c r="D27">
-        <v>40</v>
-      </c>
-      <c r="E27" s="2">
+      <c r="D27" s="3">
+        <v>40</v>
+      </c>
+      <c r="E27" s="5">
         <v>12</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="5">
         <f t="shared" si="0"/>
         <v>504</v>
       </c>
-      <c r="G27" s="3">
+      <c r="G27" s="6">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="H27" s="2">
+      <c r="H27" s="5">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="I27" s="2">
+      <c r="I27" s="8">
         <f t="shared" si="3"/>
         <v>516</v>
       </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" t="s">
+      <c r="A28" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="3">
         <v>39</v>
       </c>
-      <c r="D28">
-        <v>40</v>
-      </c>
-      <c r="E28" s="2">
+      <c r="D28" s="3">
+        <v>40</v>
+      </c>
+      <c r="E28" s="5">
         <v>10</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="5">
         <f t="shared" si="0"/>
         <v>390</v>
       </c>
-      <c r="G28" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H28" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I28" s="2">
+      <c r="G28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="8">
         <f t="shared" si="3"/>
         <v>390</v>
       </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" t="s">
+      <c r="A29" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="3">
         <v>37</v>
       </c>
-      <c r="D29">
-        <v>40</v>
-      </c>
-      <c r="E29" s="2">
+      <c r="D29" s="3">
+        <v>40</v>
+      </c>
+      <c r="E29" s="5">
         <v>8</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="5">
         <f t="shared" si="0"/>
         <v>296</v>
       </c>
-      <c r="G29" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H29" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I29" s="2">
+      <c r="G29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I29" s="8">
         <f t="shared" si="3"/>
         <v>296</v>
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" t="s">
+      <c r="A30" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="3">
         <v>41</v>
       </c>
-      <c r="D30">
-        <v>40</v>
-      </c>
-      <c r="E30" s="2">
+      <c r="D30" s="3">
+        <v>40</v>
+      </c>
+      <c r="E30" s="5">
         <v>13</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="5">
         <f t="shared" si="0"/>
         <v>533</v>
       </c>
-      <c r="G30" s="3">
+      <c r="G30" s="6">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="H30" s="2">
+      <c r="H30" s="5">
         <f t="shared" si="2"/>
         <v>6.5</v>
       </c>
-      <c r="I30" s="2">
+      <c r="I30" s="8">
         <f t="shared" si="3"/>
         <v>539.5</v>
       </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" t="s">
+      <c r="A31" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="3">
         <v>46</v>
       </c>
-      <c r="D31">
-        <v>40</v>
-      </c>
-      <c r="E31" s="2">
+      <c r="D31" s="3">
+        <v>40</v>
+      </c>
+      <c r="E31" s="5">
         <v>16</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="5">
         <f t="shared" si="0"/>
         <v>736</v>
       </c>
-      <c r="G31" s="3">
+      <c r="G31" s="6">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="H31" s="2">
+      <c r="H31" s="5">
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="I31" s="2">
+      <c r="I31" s="8">
         <f t="shared" si="3"/>
         <v>784</v>
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" t="s">
+      <c r="A32" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C32">
-        <v>40</v>
-      </c>
-      <c r="D32">
-        <v>40</v>
-      </c>
-      <c r="E32" s="2">
+      <c r="C32" s="3">
+        <v>40</v>
+      </c>
+      <c r="D32" s="3">
+        <v>40</v>
+      </c>
+      <c r="E32" s="5">
         <v>9</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="5">
         <f t="shared" si="0"/>
         <v>360</v>
       </c>
-      <c r="G32" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H32" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I32" s="2">
+      <c r="G32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I32" s="8">
         <f t="shared" si="3"/>
         <v>360</v>
       </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" t="s">
+      <c r="A33" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="3">
         <v>36</v>
       </c>
-      <c r="D33">
-        <v>40</v>
-      </c>
-      <c r="E33" s="2">
+      <c r="D33" s="3">
+        <v>40</v>
+      </c>
+      <c r="E33" s="5">
         <v>8</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="5">
         <f t="shared" si="0"/>
         <v>288</v>
       </c>
-      <c r="G33" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H33" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I33" s="2">
+      <c r="G33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I33" s="8">
         <f t="shared" si="3"/>
         <v>288</v>
       </c>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" t="s">
+      <c r="A34" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="3">
         <v>43</v>
       </c>
-      <c r="D34">
-        <v>40</v>
-      </c>
-      <c r="E34" s="2">
+      <c r="D34" s="3">
+        <v>40</v>
+      </c>
+      <c r="E34" s="5">
         <v>12</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="5">
         <f t="shared" si="0"/>
         <v>516</v>
       </c>
-      <c r="G34" s="3">
+      <c r="G34" s="6">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="H34" s="2">
+      <c r="H34" s="5">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="I34" s="2">
+      <c r="I34" s="8">
         <f t="shared" si="3"/>
         <v>534</v>
       </c>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" t="s">
+      <c r="A35" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="3">
         <v>38</v>
       </c>
-      <c r="D35">
-        <v>40</v>
-      </c>
-      <c r="E35" s="2">
+      <c r="D35" s="3">
+        <v>40</v>
+      </c>
+      <c r="E35" s="5">
         <v>10</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="5">
         <f t="shared" si="0"/>
         <v>380</v>
       </c>
-      <c r="G35" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H35" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I35" s="2">
+      <c r="G35" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I35" s="8">
         <f t="shared" si="3"/>
         <v>380</v>
       </c>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" t="s">
+      <c r="A36" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="3">
         <v>39</v>
       </c>
-      <c r="D36">
-        <v>40</v>
-      </c>
-      <c r="E36" s="2">
+      <c r="D36" s="3">
+        <v>40</v>
+      </c>
+      <c r="E36" s="5">
         <v>8</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="5">
         <f t="shared" si="0"/>
         <v>312</v>
       </c>
-      <c r="G36" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H36" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I36" s="2">
+      <c r="G36" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I36" s="8">
         <f t="shared" si="3"/>
         <v>312</v>
       </c>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" t="s">
+      <c r="A37" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="3">
         <v>42</v>
       </c>
-      <c r="D37">
-        <v>40</v>
-      </c>
-      <c r="E37" s="2">
+      <c r="D37" s="3">
+        <v>40</v>
+      </c>
+      <c r="E37" s="5">
         <v>13</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="5">
         <f t="shared" si="0"/>
         <v>546</v>
       </c>
-      <c r="G37" s="3">
+      <c r="G37" s="6">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="H37" s="2">
+      <c r="H37" s="5">
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="I37" s="2">
+      <c r="I37" s="8">
         <f t="shared" si="3"/>
         <v>559</v>
       </c>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" t="s">
+      <c r="A38" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C38">
-        <v>40</v>
-      </c>
-      <c r="D38">
-        <v>40</v>
-      </c>
-      <c r="E38" s="2">
+      <c r="C38" s="3">
+        <v>40</v>
+      </c>
+      <c r="D38" s="3">
+        <v>40</v>
+      </c>
+      <c r="E38" s="5">
         <v>9</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="5">
         <f t="shared" si="0"/>
         <v>360</v>
       </c>
-      <c r="G38" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H38" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="G38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I38" s="8">
         <f t="shared" si="3"/>
         <v>360</v>
       </c>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" t="s">
+      <c r="A39" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="3">
         <v>37</v>
       </c>
-      <c r="D39">
-        <v>40</v>
-      </c>
-      <c r="E39" s="2">
+      <c r="D39" s="3">
+        <v>40</v>
+      </c>
+      <c r="E39" s="5">
         <v>8</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="5">
         <f t="shared" si="0"/>
         <v>296</v>
       </c>
-      <c r="G39" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H39" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I39" s="2">
+      <c r="G39" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I39" s="8">
         <f t="shared" si="3"/>
         <v>296</v>
       </c>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" t="s">
+      <c r="A40" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="3">
         <v>44</v>
       </c>
-      <c r="D40">
-        <v>40</v>
-      </c>
-      <c r="E40" s="2">
+      <c r="D40" s="3">
+        <v>40</v>
+      </c>
+      <c r="E40" s="5">
         <v>12</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="5">
         <f t="shared" si="0"/>
         <v>528</v>
       </c>
-      <c r="G40" s="3">
+      <c r="G40" s="6">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="H40" s="2">
+      <c r="H40" s="5">
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="I40" s="2">
+      <c r="I40" s="8">
         <f t="shared" si="3"/>
         <v>552</v>
       </c>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" t="s">
+      <c r="A41" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="3">
         <v>45</v>
       </c>
-      <c r="D41">
-        <v>40</v>
-      </c>
-      <c r="E41" s="2">
+      <c r="D41" s="3">
+        <v>40</v>
+      </c>
+      <c r="E41" s="5">
         <v>15</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F41" s="5">
         <f t="shared" si="0"/>
         <v>675</v>
       </c>
-      <c r="G41" s="3">
+      <c r="G41" s="6">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="H41" s="2">
+      <c r="H41" s="5">
         <f t="shared" si="2"/>
         <v>37.5</v>
       </c>
-      <c r="I41" s="2">
+      <c r="I41" s="8">
         <f t="shared" si="3"/>
         <v>712.5</v>
       </c>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="1" t="s">
+      <c r="A42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C42">
-        <v>40</v>
-      </c>
-      <c r="D42">
-        <v>40</v>
-      </c>
-      <c r="E42" s="2">
+      <c r="C42" s="3">
+        <v>40</v>
+      </c>
+      <c r="D42" s="3">
+        <v>40</v>
+      </c>
+      <c r="E42" s="5">
         <v>9</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="5">
         <f t="shared" si="0"/>
         <v>360</v>
       </c>
-      <c r="G42" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H42" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I42" s="2">
+      <c r="G42" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I42" s="8">
         <f t="shared" si="3"/>
         <v>360</v>
       </c>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" t="s">
+      <c r="A43" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="3">
         <v>38</v>
       </c>
-      <c r="D43">
-        <v>40</v>
-      </c>
-      <c r="E43" s="2">
+      <c r="D43" s="3">
+        <v>40</v>
+      </c>
+      <c r="E43" s="5">
         <v>8</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F43" s="5">
         <f t="shared" si="0"/>
         <v>304</v>
       </c>
-      <c r="G43" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H43" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I43" s="2">
+      <c r="G43" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I43" s="8">
         <f t="shared" si="3"/>
         <v>304</v>
       </c>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" t="s">
+      <c r="A44" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="3">
         <v>41</v>
       </c>
-      <c r="D44">
-        <v>40</v>
-      </c>
-      <c r="E44" s="2">
+      <c r="D44" s="3">
+        <v>40</v>
+      </c>
+      <c r="E44" s="5">
         <v>12</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F44" s="5">
         <f t="shared" si="0"/>
         <v>492</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="6">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="H44" s="2">
+      <c r="H44" s="5">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="I44" s="2">
+      <c r="I44" s="8">
         <f t="shared" si="3"/>
         <v>498</v>
       </c>
     </row>
     <row r="45" spans="1:9">
-      <c r="A45" t="s">
+      <c r="A45" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="3">
         <v>39</v>
       </c>
-      <c r="D45">
-        <v>40</v>
-      </c>
-      <c r="E45" s="2">
+      <c r="D45" s="3">
+        <v>40</v>
+      </c>
+      <c r="E45" s="5">
         <v>10</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="5">
         <f t="shared" si="0"/>
         <v>390</v>
       </c>
-      <c r="G45" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H45" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I45" s="2">
+      <c r="G45" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I45" s="8">
         <f t="shared" si="3"/>
         <v>390</v>
       </c>
     </row>
     <row r="46" spans="1:9">
-      <c r="A46" t="s">
+      <c r="A46" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="3">
         <v>36</v>
       </c>
-      <c r="D46">
-        <v>40</v>
-      </c>
-      <c r="E46" s="2">
+      <c r="D46" s="3">
+        <v>40</v>
+      </c>
+      <c r="E46" s="5">
         <v>8</v>
       </c>
-      <c r="F46" s="2">
+      <c r="F46" s="5">
         <f t="shared" si="0"/>
         <v>288</v>
       </c>
-      <c r="G46" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H46" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I46" s="2">
+      <c r="G46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I46" s="8">
         <f t="shared" si="3"/>
         <v>288</v>
       </c>
     </row>
     <row r="47" spans="1:9">
-      <c r="A47" t="s">
+      <c r="A47" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="3">
         <v>43</v>
       </c>
-      <c r="D47">
-        <v>40</v>
-      </c>
-      <c r="E47" s="2">
+      <c r="D47" s="3">
+        <v>40</v>
+      </c>
+      <c r="E47" s="5">
         <v>13</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="5">
         <f t="shared" si="0"/>
         <v>559</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="6">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="H47" s="2">
+      <c r="H47" s="5">
         <f t="shared" si="2"/>
         <v>19.5</v>
       </c>
-      <c r="I47" s="2">
+      <c r="I47" s="8">
         <f t="shared" si="3"/>
         <v>578.5</v>
       </c>
     </row>
     <row r="48" spans="1:9">
-      <c r="A48" t="s">
+      <c r="A48" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C48">
-        <v>40</v>
-      </c>
-      <c r="D48">
-        <v>40</v>
-      </c>
-      <c r="E48" s="2">
+      <c r="C48" s="3">
+        <v>40</v>
+      </c>
+      <c r="D48" s="3">
+        <v>40</v>
+      </c>
+      <c r="E48" s="5">
         <v>9</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="5">
         <f t="shared" si="0"/>
         <v>360</v>
       </c>
-      <c r="G48" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H48" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I48" s="2">
+      <c r="G48" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H48" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I48" s="8">
         <f t="shared" si="3"/>
         <v>360</v>
       </c>
     </row>
     <row r="49" spans="1:9">
-      <c r="A49" t="s">
+      <c r="A49" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="3">
         <v>37</v>
       </c>
-      <c r="D49">
-        <v>40</v>
-      </c>
-      <c r="E49" s="2">
+      <c r="D49" s="3">
+        <v>40</v>
+      </c>
+      <c r="E49" s="5">
         <v>8</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="5">
         <f t="shared" si="0"/>
         <v>296</v>
       </c>
-      <c r="G49" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H49" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I49" s="2">
+      <c r="G49" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H49" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I49" s="8">
         <f t="shared" si="3"/>
         <v>296</v>
       </c>
     </row>
     <row r="50" spans="1:9">
-      <c r="A50" t="s">
+      <c r="A50" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="3">
         <v>42</v>
       </c>
-      <c r="D50">
-        <v>40</v>
-      </c>
-      <c r="E50" s="2">
+      <c r="D50" s="3">
+        <v>40</v>
+      </c>
+      <c r="E50" s="5">
         <v>12</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="5">
         <f t="shared" si="0"/>
         <v>504</v>
       </c>
-      <c r="G50" s="3">
+      <c r="G50" s="6">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="H50" s="2">
+      <c r="H50" s="5">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="I50" s="2">
+      <c r="I50" s="8">
         <f t="shared" si="3"/>
         <v>516</v>
       </c>
     </row>
     <row r="51" spans="1:9">
-      <c r="A51" t="s">
+      <c r="A51" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="3">
         <v>46</v>
       </c>
-      <c r="D51">
-        <v>40</v>
-      </c>
-      <c r="E51" s="2">
+      <c r="D51" s="3">
+        <v>40</v>
+      </c>
+      <c r="E51" s="5">
         <v>16</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F51" s="5">
         <f t="shared" si="0"/>
         <v>736</v>
       </c>
-      <c r="G51" s="3">
+      <c r="G51" s="6">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="H51" s="2">
+      <c r="H51" s="5">
         <f t="shared" si="2"/>
         <v>48</v>
       </c>
-      <c r="I51" s="2">
+      <c r="I51" s="8">
         <f t="shared" si="3"/>
         <v>784</v>
       </c>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" t="s">
+      <c r="A53" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C53">
+      <c r="B53" s="3"/>
+      <c r="C53" s="3">
         <f t="shared" ref="C53:I53" si="4">MAX(C2:C51)</f>
         <v>46</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="3">
         <f t="shared" si="4"/>
         <v>40</v>
       </c>
-      <c r="E53" s="2">
+      <c r="E53" s="5">
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53" s="5">
         <f t="shared" si="4"/>
         <v>736</v>
       </c>
-      <c r="G53">
+      <c r="G53" s="3">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="H53" s="2">
+      <c r="H53" s="5">
         <f t="shared" si="4"/>
         <v>48</v>
       </c>
-      <c r="I53" s="2">
+      <c r="I53" s="5">
         <f t="shared" si="4"/>
         <v>784</v>
       </c>
     </row>
     <row r="54" spans="1:9">
-      <c r="A54" t="s">
+      <c r="A54" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C54">
+      <c r="B54" s="3"/>
+      <c r="C54" s="3">
         <f>MIN(C2:C51)</f>
         <v>36</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="3">
         <f>MIN(D2:D51)</f>
         <v>40</v>
       </c>
-      <c r="E54" s="2">
+      <c r="E54" s="5">
         <f>MIN(E3:E52)</f>
         <v>8</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F54" s="5">
         <f>MIN(F3:F52)</f>
         <v>288</v>
       </c>
-      <c r="G54">
+      <c r="G54" s="3">
         <f>MIN(G2:G51)</f>
         <v>0</v>
       </c>
-      <c r="H54" s="2">
+      <c r="H54" s="5">
         <f>MIN(H3:H52)</f>
         <v>0</v>
       </c>
-      <c r="I54" s="2">
+      <c r="I54" s="5">
         <f>MIN(I3:I52)</f>
         <v>288</v>
       </c>
     </row>
     <row r="55" spans="1:9">
-      <c r="A55" t="s">
+      <c r="A55" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C55">
+      <c r="B55" s="3"/>
+      <c r="C55" s="3">
         <f>AVERAGE(C2:C51)</f>
         <v>40.58</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="3">
         <f>AVERAGE(D2:D51)</f>
         <v>40</v>
       </c>
-      <c r="E55" s="2">
+      <c r="E55" s="5">
         <f>AVERAGE(E4:E53)</f>
         <v>10.836734693877551</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55" s="5">
         <f>AVERAGE(F4:F53)</f>
         <v>448.0204081632653</v>
       </c>
-      <c r="G55" s="4">
+      <c r="G55" s="7">
         <f>AVERAGE(G3:G52)</f>
         <v>1.4081632653061225</v>
       </c>
-      <c r="H55" s="2">
+      <c r="H55" s="5">
         <f>AVERAGE(H4:H53)</f>
         <v>10.785714285714286</v>
       </c>
-      <c r="I55" s="2">
+      <c r="I55" s="5">
         <f>AVERAGE(I4:I53)</f>
         <v>458.80612244897958</v>
       </c>
